--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -1353,22 +1353,56 @@
       <c r="Z11" s="29" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="20">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="32" t="n"/>
-      <c r="M12" s="32" t="n"/>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Galerie Gisela Capitain</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>141</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="N12" s="33" t="n"/>
-      <c r="O12" s="34" t="n"/>
-      <c r="P12" s="33" t="n"/>
+      <c r="O12" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P12" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q12" s="33" t="n"/>
       <c r="R12" s="33" t="n"/>
       <c r="S12" s="33" t="n"/>
@@ -1381,22 +1415,56 @@
       <c r="Z12" s="29" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="20">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Carlos/Ishikawa</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>102</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="N13" s="33" t="n"/>
-      <c r="O13" s="34" t="n"/>
-      <c r="P13" s="33" t="n"/>
+      <c r="O13" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P13" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q13" s="33" t="n"/>
       <c r="R13" s="33" t="n"/>
       <c r="S13" s="33" t="n"/>
@@ -1409,22 +1477,56 @@
       <c r="Z13" s="29" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="20">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="31" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Casado Santapau</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="G14" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>13.79310344827586</v>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" s="32" t="n">
+        <v>25</v>
+      </c>
       <c r="N14" s="33" t="n"/>
-      <c r="O14" s="34" t="n"/>
-      <c r="P14" s="33" t="n"/>
+      <c r="O14" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P14" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q14" s="33" t="n"/>
       <c r="R14" s="33" t="n"/>
       <c r="S14" s="33" t="n"/>
@@ -1437,22 +1539,56 @@
       <c r="Z14" s="29" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="20">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="31" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Pedro Cera</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="L15" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" s="32" t="n">
+        <v>11</v>
+      </c>
       <c r="N15" s="33" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="33" t="n"/>
+      <c r="O15" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P15" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q15" s="33" t="n"/>
       <c r="R15" s="33" t="n"/>
       <c r="S15" s="33" t="n"/>
@@ -1465,22 +1601,56 @@
       <c r="Z15" s="29" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="20">
-      <c r="A16" s="21" t="n"/>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="31" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="31" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>James Cohan</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>247</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" s="32" t="n">
+        <v>23</v>
+      </c>
       <c r="N16" s="33" t="n"/>
-      <c r="O16" s="34" t="n"/>
-      <c r="P16" s="33" t="n"/>
+      <c r="O16" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P16" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q16" s="33" t="n"/>
       <c r="R16" s="33" t="n"/>
       <c r="S16" s="33" t="n"/>
@@ -29786,22 +29956,56 @@
       <c r="Z11" s="29" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="20">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="32" t="n"/>
-      <c r="M12" s="32" t="n"/>
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Ciaccia Levi</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="32" t="n">
+        <v>2</v>
+      </c>
       <c r="N12" s="33" t="n"/>
-      <c r="O12" s="34" t="n"/>
-      <c r="P12" s="33" t="n"/>
+      <c r="O12" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P12" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q12" s="33" t="n"/>
       <c r="R12" s="33" t="n"/>
       <c r="S12" s="33" t="n"/>
@@ -29814,22 +30018,56 @@
       <c r="Z12" s="29" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="20">
-      <c r="A13" s="38" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>Cibrián</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="32" t="n">
+        <v>2</v>
+      </c>
       <c r="N13" s="33" t="n"/>
-      <c r="O13" s="34" t="n"/>
-      <c r="P13" s="33" t="n"/>
+      <c r="O13" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P13" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q13" s="33" t="n"/>
       <c r="R13" s="33" t="n"/>
       <c r="S13" s="33" t="n"/>
@@ -29842,22 +30080,52 @@
       <c r="Z13" s="29" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="20">
-      <c r="A14" s="38" t="n"/>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>City Galerie Wien</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="31" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
+      <c r="E14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
+      <c r="L14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" s="33" t="n"/>
-      <c r="O14" s="34" t="n"/>
-      <c r="P14" s="33" t="n"/>
+      <c r="O14" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P14" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q14" s="33" t="n"/>
       <c r="R14" s="33" t="n"/>
       <c r="S14" s="33" t="n"/>
@@ -29870,22 +30138,56 @@
       <c r="Z14" s="29" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="20">
-      <c r="A15" s="38" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="31" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>Clima</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="N15" s="33" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="33" t="n"/>
+      <c r="O15" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P15" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q15" s="33" t="n"/>
       <c r="R15" s="33" t="n"/>
       <c r="S15" s="33" t="n"/>
@@ -29898,22 +30200,56 @@
       <c r="Z15" s="29" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="20">
-      <c r="A16" s="38" t="n"/>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="31" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="31" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="32" t="n">
+        <v>7</v>
+      </c>
       <c r="N16" s="33" t="n"/>
-      <c r="O16" s="34" t="n"/>
-      <c r="P16" s="33" t="n"/>
+      <c r="O16" s="34" t="n">
+        <v>46120</v>
+      </c>
+      <c r="P16" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_TRUE_NEXT_BLOCK_CLOSEOUT_APPLY_20260408T130041Z</t>
+        </is>
+      </c>
       <c r="Q16" s="33" t="n"/>
       <c r="R16" s="33" t="n"/>
       <c r="S16" s="33" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -147,7 +148,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -261,6 +262,9 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1663,22 +1667,56 @@
       <c r="Z16" s="29" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="20">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Sadie Coles HQ</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>98.30508474576271</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>280</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="L17" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="N17" s="33" t="n"/>
-      <c r="O17" s="34" t="n"/>
-      <c r="P17" s="33" t="n"/>
+      <c r="O17" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P17" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q17" s="33" t="n"/>
       <c r="R17" s="33" t="n"/>
       <c r="S17" s="33" t="n"/>
@@ -1691,22 +1729,56 @@
       <c r="Z17" s="29" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="20">
-      <c r="A18" s="21" t="n"/>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="31" t="n"/>
-      <c r="H18" s="31" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Thomas Dane Gallery</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="N18" s="33" t="n"/>
-      <c r="O18" s="34" t="n"/>
-      <c r="P18" s="33" t="n"/>
+      <c r="O18" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P18" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q18" s="33" t="n"/>
       <c r="R18" s="33" t="n"/>
       <c r="S18" s="33" t="n"/>
@@ -1719,22 +1791,56 @@
       <c r="Z18" s="29" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="20">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Dastan</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>240</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="L19" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" s="32" t="n">
+        <v>25</v>
+      </c>
       <c r="N19" s="33" t="n"/>
-      <c r="O19" s="34" t="n"/>
-      <c r="P19" s="33" t="n"/>
+      <c r="O19" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P19" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q19" s="33" t="n"/>
       <c r="R19" s="33" t="n"/>
       <c r="S19" s="33" t="n"/>
@@ -1747,22 +1853,56 @@
       <c r="Z19" s="29" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="20">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Anat Ebgi</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>160</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="J20" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="32" t="n">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="L20" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" s="32" t="n">
+        <v>23</v>
+      </c>
       <c r="N20" s="33" t="n"/>
-      <c r="O20" s="34" t="n"/>
-      <c r="P20" s="33" t="n"/>
+      <c r="O20" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P20" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q20" s="33" t="n"/>
       <c r="R20" s="33" t="n"/>
       <c r="S20" s="33" t="n"/>
@@ -1775,22 +1915,56 @@
       <c r="Z20" s="29" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="20">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="31" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Edel Assanti</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>85</v>
+      </c>
+      <c r="G21" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="32" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="L21" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="32" t="n">
+        <v>12</v>
+      </c>
       <c r="N21" s="33" t="n"/>
-      <c r="O21" s="34" t="n"/>
-      <c r="P21" s="33" t="n"/>
+      <c r="O21" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P21" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q21" s="33" t="n"/>
       <c r="R21" s="33" t="n"/>
       <c r="S21" s="33" t="n"/>
@@ -30262,22 +30436,54 @@
       <c r="Z16" s="29" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="20">
-      <c r="A17" s="38" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>Copperfield</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
+      <c r="E17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="N17" s="33" t="n"/>
-      <c r="O17" s="34" t="n"/>
-      <c r="P17" s="33" t="n"/>
+      <c r="O17" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P17" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q17" s="33" t="n"/>
       <c r="R17" s="33" t="n"/>
       <c r="S17" s="33" t="n"/>
@@ -30290,22 +30496,54 @@
       <c r="Z17" s="29" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="20">
-      <c r="A18" s="38" t="n"/>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>Coulisse Gallery</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="31" t="n"/>
-      <c r="H18" s="31" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
+      <c r="E18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="32" t="n">
+        <v>1</v>
+      </c>
       <c r="N18" s="33" t="n"/>
-      <c r="O18" s="34" t="n"/>
-      <c r="P18" s="33" t="n"/>
+      <c r="O18" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P18" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q18" s="33" t="n"/>
       <c r="R18" s="33" t="n"/>
       <c r="S18" s="33" t="n"/>
@@ -30318,22 +30556,56 @@
       <c r="Z18" s="29" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="20">
-      <c r="A19" s="38" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Damien &amp; The Love Guru</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>75</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="32" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="L19" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="32" t="n">
+        <v>9</v>
+      </c>
       <c r="N19" s="33" t="n"/>
-      <c r="O19" s="34" t="n"/>
-      <c r="P19" s="33" t="n"/>
+      <c r="O19" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P19" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q19" s="33" t="n"/>
       <c r="R19" s="33" t="n"/>
       <c r="S19" s="33" t="n"/>
@@ -30346,22 +30618,56 @@
       <c r="Z19" s="29" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="20">
-      <c r="A20" s="38" t="n"/>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>diez</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="32" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="L20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="N20" s="33" t="n"/>
-      <c r="O20" s="34" t="n"/>
-      <c r="P20" s="33" t="n"/>
+      <c r="O20" s="34" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P20" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q20" s="33" t="n"/>
       <c r="R20" s="33" t="n"/>
       <c r="S20" s="33" t="n"/>
@@ -30374,22 +30680,56 @@
       <c r="Z20" s="29" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="20">
-      <c r="A21" s="38" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="31" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>Drei</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" s="33" t="n"/>
-      <c r="O21" s="33" t="n"/>
-      <c r="P21" s="33" t="n"/>
+      <c r="O21" s="39" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P21" s="33" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_NEXT_SCOPE_BLOCK_CLOSEOUT_APPLY_20260410T000000Z</t>
+        </is>
+      </c>
       <c r="Q21" s="33" t="n"/>
       <c r="R21" s="33" t="n"/>
       <c r="S21" s="33" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -2526,22 +2526,60 @@
       <c r="Z31" s="7" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="40">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="28" t="n"/>
-      <c r="J32" s="28" t="n"/>
-      <c r="K32" s="28" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="28" t="n"/>
-      <c r="N32" s="29" t="n"/>
-      <c r="O32" s="29" t="n"/>
-      <c r="P32" s="29" t="n"/>
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>Grimm</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="C32" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="D32" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>333</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J32" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" s="28" t="n">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="L32" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="N32" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=89.19; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O32" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P32" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q32" s="29" t="n"/>
       <c r="R32" s="29" t="n"/>
       <c r="S32" s="29" t="n"/>
@@ -2554,22 +2592,58 @@
       <c r="Z32" s="7" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="40">
-      <c r="A33" s="36" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="28" t="n"/>
-      <c r="J33" s="28" t="n"/>
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>Galerie Karin Guenther</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" s="28" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="28" t="n"/>
-      <c r="N33" s="29" t="n"/>
-      <c r="O33" s="29" t="n"/>
-      <c r="P33" s="29" t="n"/>
+      <c r="L33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=0.0; exhibition_target_met=False; residual=artist_image_below_70pct(0.00) | exhibition_image_not_met(insufficient_image_candidates_after_download)</t>
+        </is>
+      </c>
+      <c r="O33" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P33" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="29" t="n"/>
       <c r="S33" s="29" t="n"/>
@@ -2582,22 +2656,60 @@
       <c r="Z33" s="7" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="40">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="28" t="n"/>
-      <c r="J34" s="28" t="n"/>
-      <c r="K34" s="28" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="29" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>Hales</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="I34" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=88.89; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O34" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P34" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q34" s="29" t="n"/>
       <c r="R34" s="29" t="n"/>
       <c r="S34" s="29" t="n"/>
@@ -2610,22 +2722,56 @@
       <c r="Z34" s="7" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="40">
-      <c r="A35" s="36" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>Hauser &amp; Wirth</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="27" t="n"/>
-      <c r="I35" s="28" t="n"/>
-      <c r="J35" s="28" t="n"/>
+      <c r="E35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="28" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="28" t="n"/>
-      <c r="N35" s="29" t="n"/>
-      <c r="O35" s="29" t="n"/>
-      <c r="P35" s="29" t="n"/>
+      <c r="L35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=0.0; exhibition_target_met=False; residual=artist_text_raw_missing | artist_image_scope_missing | exhibition_image_not_met(html_fetch_failed)</t>
+        </is>
+      </c>
+      <c r="O35" s="41" t="n">
+        <v>46133</v>
+      </c>
+      <c r="P35" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_EARLY_WORKBOOK_REFLECT_20260421</t>
+        </is>
+      </c>
       <c r="Q35" s="29" t="n"/>
       <c r="R35" s="29" t="n"/>
       <c r="S35" s="29" t="n"/>
@@ -2638,22 +2784,60 @@
       <c r="Z35" s="7" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="40">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="28" t="n"/>
-      <c r="J36" s="28" t="n"/>
-      <c r="K36" s="28" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="29" t="n"/>
-      <c r="P36" s="29" t="n"/>
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>Galerie Max Hetzler</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="D36" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>517</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J36" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="28" t="n">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="L36" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="N36" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=86.89; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O36" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P36" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q36" s="29" t="n"/>
       <c r="R36" s="29" t="n"/>
       <c r="S36" s="29" t="n"/>
@@ -20859,22 +21043,60 @@
       <c r="Z32" s="7" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="40">
-      <c r="A33" s="35" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="28" t="n"/>
-      <c r="J33" s="28" t="n"/>
-      <c r="K33" s="28" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="28" t="n"/>
-      <c r="N33" s="29" t="n"/>
-      <c r="O33" s="29" t="n"/>
-      <c r="P33" s="29" t="n"/>
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>Magenta Plains</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J33" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L33" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M33" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="N33" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=100.0; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O33" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P33" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q33" s="29" t="n"/>
       <c r="R33" s="29" t="n"/>
       <c r="S33" s="29" t="n"/>
@@ -20887,22 +21109,60 @@
       <c r="Z33" s="7" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="40">
-      <c r="A34" s="35" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="28" t="n"/>
-      <c r="J34" s="28" t="n"/>
-      <c r="K34" s="28" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="29" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>Margot Samel</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I34" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="J34" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" s="28" t="n">
+        <v>41.1764705882353</v>
+      </c>
+      <c r="L34" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="N34" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=88.89; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O34" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P34" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q34" s="29" t="n"/>
       <c r="R34" s="29" t="n"/>
       <c r="S34" s="29" t="n"/>
@@ -20915,22 +21175,60 @@
       <c r="Z34" s="7" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="40">
-      <c r="A35" s="35" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="27" t="n"/>
-      <c r="I35" s="28" t="n"/>
-      <c r="J35" s="28" t="n"/>
-      <c r="K35" s="28" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="28" t="n"/>
-      <c r="N35" s="29" t="n"/>
-      <c r="O35" s="29" t="n"/>
-      <c r="P35" s="29" t="n"/>
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>max goelitz</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C35" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>235</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" s="28" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="L35" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N35" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=55.0; exhibition_target_met=True; residual=artist_image_below_70pct(55.00)</t>
+        </is>
+      </c>
+      <c r="O35" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P35" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q35" s="29" t="n"/>
       <c r="R35" s="29" t="n"/>
       <c r="S35" s="29" t="n"/>
@@ -20943,22 +21241,60 @@
       <c r="Z35" s="7" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="40">
-      <c r="A36" s="35" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="28" t="n"/>
-      <c r="J36" s="28" t="n"/>
-      <c r="K36" s="28" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="29" t="n"/>
-      <c r="P36" s="29" t="n"/>
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>Nicoletti</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=0.0; exhibition_target_met=False; residual=artist_image_below_70pct(0.00) | exhibition_image_not_met(insufficient_image_candidates_after_download)</t>
+        </is>
+      </c>
+      <c r="O36" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P36" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q36" s="29" t="n"/>
       <c r="R36" s="29" t="n"/>
       <c r="S36" s="29" t="n"/>
@@ -20971,22 +21307,60 @@
       <c r="Z36" s="7" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="40">
-      <c r="A37" s="35" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="28" t="n"/>
-      <c r="J37" s="28" t="n"/>
-      <c r="K37" s="28" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="28" t="n"/>
-      <c r="N37" s="29" t="n"/>
-      <c r="O37" s="29" t="n"/>
-      <c r="P37" s="29" t="n"/>
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>Öktem Aykut</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L37" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="N37" s="29" t="inlineStr">
+        <is>
+          <t>early_review_20260421; artist_target_pct=70.0; exhibition_target_met=True; residual=none</t>
+        </is>
+      </c>
+      <c r="O37" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P37" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_CLOSEOUT_ARTIST_SOURCE_REAPPLY_20260422T0015Z</t>
+        </is>
+      </c>
       <c r="Q37" s="29" t="n"/>
       <c r="R37" s="29" t="n"/>
       <c r="S37" s="29" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -2850,22 +2850,56 @@
       <c r="Z36" s="7" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="40">
-      <c r="A37" s="36" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="28" t="n"/>
-      <c r="J37" s="28" t="n"/>
-      <c r="K37" s="28" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="28" t="n"/>
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>Hollybush Gardens</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N37" s="29" t="n"/>
-      <c r="O37" s="29" t="n"/>
-      <c r="P37" s="29" t="n"/>
+      <c r="O37" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P37" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q37" s="29" t="n"/>
       <c r="R37" s="29" t="n"/>
       <c r="S37" s="29" t="n"/>
@@ -2878,22 +2912,56 @@
       <c r="Z37" s="7" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="40">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="28" t="n"/>
-      <c r="J38" s="28" t="n"/>
-      <c r="K38" s="28" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="28" t="n"/>
+      <c r="A38" s="36" t="inlineStr">
+        <is>
+          <t>Pippy Houldsworth Gallery</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K38" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L38" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="M38" s="28" t="n">
+        <v>15</v>
+      </c>
       <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
-      <c r="P38" s="29" t="n"/>
+      <c r="O38" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P38" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q38" s="29" t="n"/>
       <c r="R38" s="29" t="n"/>
       <c r="S38" s="29" t="n"/>
@@ -2906,22 +2974,56 @@
       <c r="Z38" s="7" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="40">
-      <c r="A39" s="36" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-      <c r="I39" s="28" t="n"/>
-      <c r="J39" s="28" t="n"/>
-      <c r="K39" s="28" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="28" t="n"/>
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t>Xavier Hufkens</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>265</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="L39" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="28" t="n">
+        <v>2</v>
+      </c>
       <c r="N39" s="29" t="n"/>
-      <c r="O39" s="29" t="n"/>
-      <c r="P39" s="29" t="n"/>
+      <c r="O39" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P39" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="29" t="n"/>
       <c r="S39" s="29" t="n"/>
@@ -2934,22 +3036,56 @@
       <c r="Z39" s="7" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="40">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="28" t="n"/>
-      <c r="J40" s="28" t="n"/>
-      <c r="K40" s="28" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="28" t="n"/>
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>i8 Gallery</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J40" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="28" t="n">
+        <v>54.54545454545455</v>
+      </c>
+      <c r="L40" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="M40" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N40" s="29" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
+      <c r="O40" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P40" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q40" s="29" t="n"/>
       <c r="R40" s="29" t="n"/>
       <c r="S40" s="29" t="n"/>
@@ -2962,22 +3098,56 @@
       <c r="Z40" s="7" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="40">
-      <c r="A41" s="36" t="n"/>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="28" t="n"/>
-      <c r="J41" s="28" t="n"/>
-      <c r="K41" s="28" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="28" t="n"/>
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>Ingleby</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="C41" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N41" s="29" t="n"/>
-      <c r="O41" s="29" t="n"/>
-      <c r="P41" s="29" t="n"/>
+      <c r="O41" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P41" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q41" s="29" t="n"/>
       <c r="R41" s="29" t="n"/>
       <c r="S41" s="29" t="n"/>
@@ -21373,22 +21543,56 @@
       <c r="Z37" s="7" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="40">
-      <c r="A38" s="35" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="28" t="n"/>
-      <c r="J38" s="28" t="n"/>
-      <c r="K38" s="28" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="28" t="n"/>
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>Paulina Caspari</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="L38" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="M38" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
-      <c r="P38" s="29" t="n"/>
+      <c r="O38" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P38" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q38" s="29" t="n"/>
       <c r="R38" s="29" t="n"/>
       <c r="S38" s="29" t="n"/>
@@ -21401,22 +21605,54 @@
       <c r="Z38" s="7" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="40">
-      <c r="A39" s="35" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>Petrine</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-      <c r="I39" s="28" t="n"/>
-      <c r="J39" s="28" t="n"/>
-      <c r="K39" s="28" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="28" t="n"/>
+      <c r="E39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="29" t="n"/>
-      <c r="O39" s="29" t="n"/>
-      <c r="P39" s="29" t="n"/>
+      <c r="O39" s="41" t="n">
+        <v>46134</v>
+      </c>
+      <c r="P39" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422</t>
+        </is>
+      </c>
       <c r="Q39" s="29" t="n"/>
       <c r="R39" s="29" t="n"/>
       <c r="S39" s="29" t="n"/>
@@ -21429,22 +21665,56 @@
       <c r="Z39" s="7" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="40">
-      <c r="A40" s="35" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="28" t="n"/>
-      <c r="J40" s="28" t="n"/>
-      <c r="K40" s="28" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="28" t="n"/>
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>Rose Easton</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="M40" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N40" s="29" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
+      <c r="O40" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P40" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q40" s="29" t="n"/>
       <c r="R40" s="29" t="n"/>
       <c r="S40" s="29" t="n"/>
@@ -21457,22 +21727,56 @@
       <c r="Z40" s="7" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="40">
-      <c r="A41" s="35" t="n"/>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="28" t="n"/>
-      <c r="J41" s="28" t="n"/>
-      <c r="K41" s="28" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="28" t="n"/>
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>Schiefe Zähne</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="J41" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K41" s="28" t="n">
+        <v>44.11764705882353</v>
+      </c>
+      <c r="L41" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="M41" s="28" t="n">
+        <v>25</v>
+      </c>
       <c r="N41" s="29" t="n"/>
-      <c r="O41" s="29" t="n"/>
-      <c r="P41" s="29" t="n"/>
+      <c r="O41" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P41" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q41" s="29" t="n"/>
       <c r="R41" s="29" t="n"/>
       <c r="S41" s="29" t="n"/>
@@ -21485,22 +21789,54 @@
       <c r="Z41" s="7" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="40">
-      <c r="A42" s="35" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>Silke Lindner</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
-      <c r="H42" s="27" t="n"/>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="28" t="n"/>
-      <c r="K42" s="28" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="28" t="n"/>
+      <c r="E42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N42" s="29" t="n"/>
-      <c r="O42" s="29" t="n"/>
-      <c r="P42" s="29" t="n"/>
+      <c r="O42" s="41" t="n">
+        <v>46136</v>
+      </c>
+      <c r="P42" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_RAW_REBUILD_VERIFY_FIRST_20260422_STEP18_APPLY</t>
+        </is>
+      </c>
       <c r="Q42" s="29" t="n"/>
       <c r="R42" s="29" t="n"/>
       <c r="S42" s="29" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -3160,22 +3160,56 @@
       <c r="Z41" s="7" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="40">
-      <c r="A42" s="36" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
-      <c r="H42" s="27" t="n"/>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="28" t="n"/>
-      <c r="K42" s="28" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="28" t="n"/>
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>Alison Jacques</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="D42" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>294</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N42" s="29" t="n"/>
-      <c r="O42" s="29" t="n"/>
-      <c r="P42" s="29" t="n"/>
+      <c r="O42" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P42" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q42" s="29" t="n"/>
       <c r="R42" s="29" t="n"/>
       <c r="S42" s="29" t="n"/>
@@ -3188,22 +3222,56 @@
       <c r="Z42" s="7" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="40">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
-      <c r="I43" s="28" t="n"/>
-      <c r="J43" s="28" t="n"/>
-      <c r="K43" s="28" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="28" t="n"/>
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>Almine Rech</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D43" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="28" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="L43" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N43" s="29" t="n"/>
-      <c r="O43" s="29" t="n"/>
-      <c r="P43" s="29" t="n"/>
+      <c r="O43" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P43" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q43" s="29" t="n"/>
       <c r="R43" s="29" t="n"/>
       <c r="S43" s="29" t="n"/>
@@ -3216,22 +3284,56 @@
       <c r="Z43" s="7" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="40">
-      <c r="A44" s="36" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="27" t="n"/>
-      <c r="I44" s="28" t="n"/>
-      <c r="J44" s="28" t="n"/>
-      <c r="K44" s="28" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="28" t="n"/>
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>David Zwirner</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D44" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>640</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" s="28" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="L44" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M44" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="N44" s="29" t="n"/>
-      <c r="O44" s="29" t="n"/>
-      <c r="P44" s="29" t="n"/>
+      <c r="O44" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P44" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q44" s="29" t="n"/>
       <c r="R44" s="29" t="n"/>
       <c r="S44" s="29" t="n"/>
@@ -3244,22 +3346,56 @@
       <c r="Z44" s="7" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="40">
-      <c r="A45" s="36" t="n"/>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="27" t="n"/>
-      <c r="I45" s="28" t="n"/>
-      <c r="J45" s="28" t="n"/>
-      <c r="K45" s="28" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="28" t="n"/>
+      <c r="A45" s="36" t="inlineStr">
+        <is>
+          <t>Esther Schipper</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>265</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="L45" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M45" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N45" s="29" t="n"/>
-      <c r="O45" s="29" t="n"/>
-      <c r="P45" s="29" t="n"/>
+      <c r="O45" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P45" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q45" s="29" t="n"/>
       <c r="R45" s="29" t="n"/>
       <c r="S45" s="29" t="n"/>
@@ -3272,22 +3408,56 @@
       <c r="Z45" s="7" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="40">
-      <c r="A46" s="36" t="n"/>
-      <c r="B46" s="27" t="n"/>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="27" t="n"/>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
-      <c r="H46" s="27" t="n"/>
-      <c r="I46" s="28" t="n"/>
-      <c r="J46" s="28" t="n"/>
-      <c r="K46" s="28" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="28" t="n"/>
+      <c r="A46" s="36" t="inlineStr">
+        <is>
+          <t>Francesca Minini</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="D46" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>162</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L46" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N46" s="29" t="n"/>
-      <c r="O46" s="29" t="n"/>
-      <c r="P46" s="29" t="n"/>
+      <c r="O46" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P46" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q46" s="29" t="n"/>
       <c r="R46" s="29" t="n"/>
       <c r="S46" s="29" t="n"/>
@@ -21849,22 +22019,56 @@
       <c r="Z42" s="7" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="40">
-      <c r="A43" s="35" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
-      <c r="I43" s="28" t="n"/>
-      <c r="J43" s="28" t="n"/>
-      <c r="K43" s="28" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="28" t="n"/>
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>56 Henry</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D43" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>109</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="J43" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="28" t="n">
+        <v>47.05882352941177</v>
+      </c>
+      <c r="L43" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" s="28" t="n">
+        <v>17</v>
+      </c>
       <c r="N43" s="29" t="n"/>
-      <c r="O43" s="29" t="n"/>
-      <c r="P43" s="29" t="n"/>
+      <c r="O43" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P43" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q43" s="29" t="n"/>
       <c r="R43" s="29" t="n"/>
       <c r="S43" s="29" t="n"/>
@@ -21877,22 +22081,56 @@
       <c r="Z43" s="7" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="40">
-      <c r="A44" s="35" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="27" t="n"/>
-      <c r="I44" s="28" t="n"/>
-      <c r="J44" s="28" t="n"/>
-      <c r="K44" s="28" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="28" t="n"/>
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>Sophie Tappeiner</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="G44" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="28" t="n">
+        <v>15</v>
+      </c>
       <c r="N44" s="29" t="n"/>
-      <c r="O44" s="29" t="n"/>
-      <c r="P44" s="29" t="n"/>
+      <c r="O44" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P44" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q44" s="29" t="n"/>
       <c r="R44" s="29" t="n"/>
       <c r="S44" s="29" t="n"/>
@@ -21905,22 +22143,56 @@
       <c r="Z44" s="7" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="40">
-      <c r="A45" s="35" t="n"/>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="27" t="n"/>
-      <c r="I45" s="28" t="n"/>
-      <c r="J45" s="28" t="n"/>
-      <c r="K45" s="28" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="28" t="n"/>
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>Suprainfinit</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="F45" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="L45" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M45" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N45" s="29" t="n"/>
-      <c r="O45" s="29" t="n"/>
-      <c r="P45" s="29" t="n"/>
+      <c r="O45" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P45" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q45" s="29" t="n"/>
       <c r="R45" s="29" t="n"/>
       <c r="S45" s="29" t="n"/>
@@ -21933,22 +22205,56 @@
       <c r="Z45" s="7" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="40">
-      <c r="A46" s="35" t="n"/>
-      <c r="B46" s="27" t="n"/>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="27" t="n"/>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
-      <c r="H46" s="27" t="n"/>
-      <c r="I46" s="28" t="n"/>
-      <c r="J46" s="28" t="n"/>
-      <c r="K46" s="28" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="28" t="n"/>
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>Tabula Rasa Gallery</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="D46" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N46" s="29" t="n"/>
-      <c r="O46" s="29" t="n"/>
-      <c r="P46" s="29" t="n"/>
+      <c r="O46" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P46" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q46" s="29" t="n"/>
       <c r="R46" s="29" t="n"/>
       <c r="S46" s="29" t="n"/>
@@ -21961,22 +22267,56 @@
       <c r="Z46" s="7" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="40">
-      <c r="A47" s="35" t="n"/>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="28" t="n"/>
-      <c r="J47" s="28" t="n"/>
-      <c r="K47" s="28" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="28" t="n"/>
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>Tiwani Contemporary</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D47" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="N47" s="29" t="n"/>
-      <c r="O47" s="29" t="n"/>
-      <c r="P47" s="29" t="n"/>
+      <c r="O47" s="41" t="n">
+        <v>46137</v>
+      </c>
+      <c r="P47" s="29" t="inlineStr">
+        <is>
+          <t>p3n10r1</t>
+        </is>
+      </c>
       <c r="Q47" s="29" t="n"/>
       <c r="R47" s="29" t="n"/>
       <c r="S47" s="29" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -3470,22 +3470,56 @@
       <c r="Z46" s="7" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="40">
-      <c r="A47" s="36" t="n"/>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="28" t="n"/>
-      <c r="J47" s="28" t="n"/>
-      <c r="K47" s="28" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="28" t="n"/>
+      <c r="A47" s="36" t="inlineStr">
+        <is>
+          <t>Taka Ishii Gallery</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="L47" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N47" s="29" t="n"/>
-      <c r="O47" s="29" t="n"/>
-      <c r="P47" s="29" t="n"/>
+      <c r="O47" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P47" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q47" s="29" t="n"/>
       <c r="R47" s="29" t="n"/>
       <c r="S47" s="29" t="n"/>
@@ -3498,22 +3532,56 @@
       <c r="Z47" s="7" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="40">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
-      <c r="H48" s="27" t="n"/>
-      <c r="I48" s="28" t="n"/>
-      <c r="J48" s="28" t="n"/>
-      <c r="K48" s="28" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="28" t="n"/>
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>Jhaveri Contemporary</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J48" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="L48" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N48" s="29" t="n"/>
-      <c r="O48" s="29" t="n"/>
-      <c r="P48" s="29" t="n"/>
+      <c r="O48" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P48" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q48" s="29" t="n"/>
       <c r="R48" s="29" t="n"/>
       <c r="S48" s="29" t="n"/>
@@ -3526,22 +3594,56 @@
       <c r="Z48" s="7" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="40">
-      <c r="A49" s="36" t="n"/>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="28" t="n"/>
-      <c r="J49" s="28" t="n"/>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="28" t="n"/>
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>Johyun Gallery</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="C49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="D49" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J49" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L49" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" s="28" t="n">
+        <v>16</v>
+      </c>
       <c r="N49" s="29" t="n"/>
-      <c r="O49" s="29" t="n"/>
-      <c r="P49" s="29" t="n"/>
+      <c r="O49" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P49" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q49" s="29" t="n"/>
       <c r="R49" s="29" t="n"/>
       <c r="S49" s="29" t="n"/>
@@ -3554,22 +3656,56 @@
       <c r="Z49" s="7" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="40">
-      <c r="A50" s="36" t="n"/>
-      <c r="B50" s="27" t="n"/>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="27" t="n"/>
-      <c r="E50" s="27" t="n"/>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="27" t="n"/>
-      <c r="H50" s="27" t="n"/>
-      <c r="I50" s="28" t="n"/>
-      <c r="J50" s="28" t="n"/>
-      <c r="K50" s="28" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="28" t="n"/>
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>Kalfayan Galleries</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="28" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="L50" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N50" s="29" t="n"/>
-      <c r="O50" s="29" t="n"/>
-      <c r="P50" s="29" t="n"/>
+      <c r="O50" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P50" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q50" s="29" t="n"/>
       <c r="R50" s="29" t="n"/>
       <c r="S50" s="29" t="n"/>
@@ -3582,22 +3718,56 @@
       <c r="Z50" s="7" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="40">
-      <c r="A51" s="36" t="n"/>
-      <c r="B51" s="27" t="n"/>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="27" t="n"/>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
-      <c r="H51" s="27" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="28" t="n"/>
-      <c r="K51" s="28" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="28" t="n"/>
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>Karma</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="D51" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>66</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J51" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K51" s="28" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="L51" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N51" s="29" t="n"/>
-      <c r="O51" s="29" t="n"/>
-      <c r="P51" s="29" t="n"/>
+      <c r="O51" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P51" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q51" s="29" t="n"/>
       <c r="R51" s="29" t="n"/>
       <c r="S51" s="29" t="n"/>
@@ -22329,22 +22499,56 @@
       <c r="Z47" s="7" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="40">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
-      <c r="H48" s="27" t="n"/>
-      <c r="I48" s="28" t="n"/>
-      <c r="J48" s="28" t="n"/>
-      <c r="K48" s="28" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="28" t="n"/>
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>Turnus</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="J48" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="L48" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>12</v>
+      </c>
       <c r="N48" s="29" t="n"/>
-      <c r="O48" s="29" t="n"/>
-      <c r="P48" s="29" t="n"/>
+      <c r="O48" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P48" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q48" s="29" t="n"/>
       <c r="R48" s="29" t="n"/>
       <c r="S48" s="29" t="n"/>
@@ -22357,22 +22561,54 @@
       <c r="Z48" s="7" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="40">
-      <c r="A49" s="35" t="n"/>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>Valerie's Factory</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="28" t="n"/>
-      <c r="J49" s="28" t="n"/>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="28" t="n"/>
+      <c r="E49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" s="29" t="n"/>
-      <c r="O49" s="29" t="n"/>
-      <c r="P49" s="29" t="n"/>
+      <c r="O49" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P49" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q49" s="29" t="n"/>
       <c r="R49" s="29" t="n"/>
       <c r="S49" s="29" t="n"/>
@@ -22385,22 +22621,56 @@
       <c r="Z49" s="7" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="40">
-      <c r="A50" s="35" t="n"/>
-      <c r="B50" s="27" t="n"/>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="27" t="n"/>
-      <c r="E50" s="27" t="n"/>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="27" t="n"/>
-      <c r="H50" s="27" t="n"/>
-      <c r="I50" s="28" t="n"/>
-      <c r="J50" s="28" t="n"/>
-      <c r="K50" s="28" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="28" t="n"/>
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>Vanguard Gallery</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="C50" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="D50" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>156</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="28" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="L50" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" s="28" t="n">
+        <v>9</v>
+      </c>
       <c r="N50" s="29" t="n"/>
-      <c r="O50" s="29" t="n"/>
-      <c r="P50" s="29" t="n"/>
+      <c r="O50" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P50" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q50" s="29" t="n"/>
       <c r="R50" s="29" t="n"/>
       <c r="S50" s="29" t="n"/>
@@ -22413,22 +22683,56 @@
       <c r="Z50" s="7" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="40">
-      <c r="A51" s="35" t="n"/>
-      <c r="B51" s="27" t="n"/>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="27" t="n"/>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
-      <c r="H51" s="27" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="28" t="n"/>
-      <c r="K51" s="28" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="28" t="n"/>
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>Voloshyn Gallery</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="C51" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="D51" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="L51" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N51" s="29" t="n"/>
-      <c r="O51" s="29" t="n"/>
-      <c r="P51" s="29" t="n"/>
+      <c r="O51" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P51" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q51" s="29" t="n"/>
       <c r="R51" s="29" t="n"/>
       <c r="S51" s="29" t="n"/>
@@ -22441,22 +22745,56 @@
       <c r="Z51" s="7" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="40">
-      <c r="A52" s="35" t="n"/>
-      <c r="B52" s="27" t="n"/>
-      <c r="C52" s="27" t="n"/>
-      <c r="D52" s="27" t="n"/>
-      <c r="E52" s="27" t="n"/>
-      <c r="F52" s="27" t="n"/>
-      <c r="G52" s="27" t="n"/>
-      <c r="H52" s="27" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="28" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="28" t="n"/>
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="C52" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="D52" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="J52" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>31</v>
+      </c>
       <c r="N52" s="29" t="n"/>
-      <c r="O52" s="29" t="n"/>
-      <c r="P52" s="29" t="n"/>
+      <c r="O52" s="41" t="n">
+        <v>46144</v>
+      </c>
+      <c r="P52" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_XLSX_UPDATE_20260502T000000Z</t>
+        </is>
+      </c>
       <c r="Q52" s="29" t="n"/>
       <c r="R52" s="29" t="n"/>
       <c r="S52" s="29" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -3780,22 +3780,56 @@
       <c r="Z51" s="7" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="40">
-      <c r="A52" s="36" t="n"/>
-      <c r="B52" s="27" t="n"/>
-      <c r="C52" s="27" t="n"/>
-      <c r="D52" s="27" t="n"/>
-      <c r="E52" s="27" t="n"/>
-      <c r="F52" s="27" t="n"/>
-      <c r="G52" s="27" t="n"/>
-      <c r="H52" s="27" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="28" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="28" t="n"/>
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>Galerie Krinzinger</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C52" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D52" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>563</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="J52" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="L52" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>21</v>
+      </c>
       <c r="N52" s="29" t="n"/>
-      <c r="O52" s="29" t="n"/>
-      <c r="P52" s="29" t="n"/>
+      <c r="O52" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P52" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q52" s="29" t="n"/>
       <c r="R52" s="29" t="n"/>
       <c r="S52" s="29" t="n"/>
@@ -3808,22 +3842,56 @@
       <c r="Z52" s="7" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="40">
-      <c r="A53" s="36" t="n"/>
-      <c r="B53" s="27" t="n"/>
-      <c r="C53" s="27" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="28" t="n"/>
-      <c r="J53" s="28" t="n"/>
-      <c r="K53" s="28" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="28" t="n"/>
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>Galerie Peter Kilchmann</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="D53" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>411</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J53" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="L53" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="M53" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N53" s="29" t="n"/>
-      <c r="O53" s="29" t="n"/>
-      <c r="P53" s="29" t="n"/>
+      <c r="O53" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P53" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q53" s="29" t="n"/>
       <c r="R53" s="29" t="n"/>
       <c r="S53" s="29" t="n"/>
@@ -3836,22 +3904,60 @@
       <c r="Z53" s="7" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="40">
-      <c r="A54" s="36" t="n"/>
-      <c r="B54" s="27" t="n"/>
-      <c r="C54" s="27" t="n"/>
-      <c r="D54" s="27" t="n"/>
-      <c r="E54" s="27" t="n"/>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
-      <c r="H54" s="27" t="n"/>
-      <c r="I54" s="28" t="n"/>
-      <c r="J54" s="28" t="n"/>
-      <c r="K54" s="28" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="28" t="n"/>
-      <c r="N54" s="29" t="n"/>
-      <c r="O54" s="29" t="n"/>
-      <c r="P54" s="29" t="n"/>
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>Galerie Poggi</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="29" t="inlineStr">
+        <is>
+          <t>human_skip_after_verify_first</t>
+        </is>
+      </c>
+      <c r="O54" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P54" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q54" s="29" t="n"/>
       <c r="R54" s="29" t="n"/>
       <c r="S54" s="29" t="n"/>
@@ -3864,22 +3970,56 @@
       <c r="Z54" s="7" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="40">
-      <c r="A55" s="36" t="n"/>
-      <c r="B55" s="27" t="n"/>
-      <c r="C55" s="27" t="n"/>
+      <c r="A55" s="36" t="inlineStr">
+        <is>
+          <t>Galleria Lorcan O'Neill</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D55" s="27" t="n"/>
-      <c r="E55" s="27" t="n"/>
-      <c r="F55" s="27" t="n"/>
-      <c r="G55" s="27" t="n"/>
-      <c r="H55" s="27" t="n"/>
-      <c r="I55" s="28" t="n"/>
-      <c r="J55" s="28" t="n"/>
+      <c r="E55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="K55" s="28" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="28" t="n"/>
-      <c r="N55" s="29" t="n"/>
-      <c r="O55" s="29" t="n"/>
-      <c r="P55" s="29" t="n"/>
+      <c r="L55" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="29" t="inlineStr">
+        <is>
+          <t>human_skip_after_verify_first</t>
+        </is>
+      </c>
+      <c r="O55" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P55" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q55" s="29" t="n"/>
       <c r="R55" s="29" t="n"/>
       <c r="S55" s="29" t="n"/>
@@ -3892,22 +4032,56 @@
       <c r="Z55" s="7" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="40">
-      <c r="A56" s="36" t="n"/>
-      <c r="B56" s="27" t="n"/>
-      <c r="C56" s="27" t="n"/>
-      <c r="D56" s="27" t="n"/>
-      <c r="E56" s="27" t="n"/>
-      <c r="F56" s="27" t="n"/>
-      <c r="G56" s="27" t="n"/>
-      <c r="H56" s="27" t="n"/>
-      <c r="I56" s="28" t="n"/>
-      <c r="J56" s="28" t="n"/>
-      <c r="K56" s="28" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="28" t="n"/>
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>Galleria Massimo Minini</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C56" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D56" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>444</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J56" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v>36.66666666666666</v>
+      </c>
+      <c r="L56" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="M56" s="28" t="n">
+        <v>25</v>
+      </c>
       <c r="N56" s="29" t="n"/>
-      <c r="O56" s="29" t="n"/>
-      <c r="P56" s="29" t="n"/>
+      <c r="O56" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P56" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q56" s="29" t="n"/>
       <c r="R56" s="29" t="n"/>
       <c r="S56" s="29" t="n"/>
@@ -3920,22 +4094,56 @@
       <c r="Z56" s="7" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="40">
-      <c r="A57" s="36" t="n"/>
-      <c r="B57" s="27" t="n"/>
-      <c r="C57" s="27" t="n"/>
-      <c r="D57" s="27" t="n"/>
-      <c r="E57" s="27" t="n"/>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="27" t="n"/>
-      <c r="H57" s="27" t="n"/>
-      <c r="I57" s="28" t="n"/>
-      <c r="J57" s="28" t="n"/>
-      <c r="K57" s="28" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="28" t="n"/>
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>Jane Lombard</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="D57" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>101</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="H57" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J57" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" s="28" t="n">
+        <v>81.81818181818181</v>
+      </c>
+      <c r="L57" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M57" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N57" s="29" t="n"/>
-      <c r="O57" s="29" t="n"/>
-      <c r="P57" s="29" t="n"/>
+      <c r="O57" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P57" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q57" s="29" t="n"/>
       <c r="R57" s="29" t="n"/>
       <c r="S57" s="29" t="n"/>
@@ -3948,22 +4156,56 @@
       <c r="Z57" s="7" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="40">
-      <c r="A58" s="36" t="n"/>
-      <c r="B58" s="27" t="n"/>
-      <c r="C58" s="27" t="n"/>
-      <c r="D58" s="27" t="n"/>
-      <c r="E58" s="27" t="n"/>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="27" t="n"/>
-      <c r="H58" s="27" t="n"/>
-      <c r="I58" s="28" t="n"/>
-      <c r="J58" s="28" t="n"/>
-      <c r="K58" s="28" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="28" t="n"/>
+      <c r="A58" s="36" t="inlineStr">
+        <is>
+          <t>Josh Lilley</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="C58" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D58" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="28" t="n">
+        <v>2</v>
+      </c>
       <c r="N58" s="29" t="n"/>
-      <c r="O58" s="29" t="n"/>
-      <c r="P58" s="29" t="n"/>
+      <c r="O58" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P58" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q58" s="29" t="n"/>
       <c r="R58" s="29" t="n"/>
       <c r="S58" s="29" t="n"/>
@@ -3976,22 +4218,56 @@
       <c r="Z58" s="7" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="40">
-      <c r="A59" s="36" t="n"/>
-      <c r="B59" s="27" t="n"/>
-      <c r="C59" s="27" t="n"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="28" t="n"/>
-      <c r="J59" s="28" t="n"/>
-      <c r="K59" s="28" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="28" t="n"/>
+      <c r="A59" s="36" t="inlineStr">
+        <is>
+          <t>Kasmin</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="C59" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J59" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="L59" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M59" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="N59" s="29" t="n"/>
-      <c r="O59" s="29" t="n"/>
-      <c r="P59" s="29" t="n"/>
+      <c r="O59" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P59" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q59" s="29" t="n"/>
       <c r="R59" s="29" t="n"/>
       <c r="S59" s="29" t="n"/>
@@ -22807,22 +23083,56 @@
       <c r="Z52" s="7" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="40">
-      <c r="A53" s="35" t="n"/>
-      <c r="B53" s="27" t="n"/>
-      <c r="C53" s="27" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="28" t="n"/>
-      <c r="J53" s="28" t="n"/>
-      <c r="K53" s="28" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="28" t="n"/>
+      <c r="A53" s="35" t="inlineStr">
+        <is>
+          <t>Yeo Workshop</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="C53" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="D53" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="J53" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v>76.92307692307692</v>
+      </c>
+      <c r="L53" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" s="28" t="n">
+        <v>12</v>
+      </c>
       <c r="N53" s="29" t="n"/>
-      <c r="O53" s="29" t="n"/>
-      <c r="P53" s="29" t="n"/>
+      <c r="O53" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P53" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q53" s="29" t="n"/>
       <c r="R53" s="29" t="n"/>
       <c r="S53" s="29" t="n"/>
@@ -22835,22 +23145,56 @@
       <c r="Z53" s="7" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="40">
-      <c r="A54" s="35" t="n"/>
-      <c r="B54" s="27" t="n"/>
-      <c r="C54" s="27" t="n"/>
-      <c r="D54" s="27" t="n"/>
-      <c r="E54" s="27" t="n"/>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
-      <c r="H54" s="27" t="n"/>
-      <c r="I54" s="28" t="n"/>
-      <c r="J54" s="28" t="n"/>
-      <c r="K54" s="28" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="28" t="n"/>
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>YveYang Gallery</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="D54" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L54" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M54" s="28" t="n">
+        <v>4</v>
+      </c>
       <c r="N54" s="29" t="n"/>
-      <c r="O54" s="29" t="n"/>
-      <c r="P54" s="29" t="n"/>
+      <c r="O54" s="41" t="n">
+        <v>46151</v>
+      </c>
+      <c r="P54" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK6_SKIP_REFLECT_20260509</t>
+        </is>
+      </c>
       <c r="Q54" s="29" t="n"/>
       <c r="R54" s="29" t="n"/>
       <c r="S54" s="29" t="n"/>

--- a/data/gallery_lists/rag_gellery_breakdown_master.xlsx
+++ b/data/gallery_lists/rag_gellery_breakdown_master.xlsx
@@ -4280,22 +4280,56 @@
       <c r="Z59" s="7" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="40">
-      <c r="A60" s="36" t="n"/>
-      <c r="B60" s="27" t="n"/>
-      <c r="C60" s="27" t="n"/>
-      <c r="D60" s="27" t="n"/>
-      <c r="E60" s="27" t="n"/>
-      <c r="F60" s="27" t="n"/>
-      <c r="G60" s="27" t="n"/>
-      <c r="H60" s="27" t="n"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="28" t="n"/>
-      <c r="K60" s="28" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="28" t="n"/>
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>Sean Kelly</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="C60" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="D60" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>179</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="I60" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="J60" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" s="28" t="n">
+        <v>47.05882352941177</v>
+      </c>
+      <c r="L60" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M60" s="28" t="n">
+        <v>17</v>
+      </c>
       <c r="N60" s="29" t="n"/>
-      <c r="O60" s="29" t="n"/>
-      <c r="P60" s="29" t="n"/>
+      <c r="O60" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P60" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q60" s="29" t="n"/>
       <c r="R60" s="29" t="n"/>
       <c r="S60" s="29" t="n"/>
@@ -4308,22 +4342,56 @@
       <c r="Z60" s="7" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="40">
-      <c r="A61" s="36" t="n"/>
-      <c r="B61" s="27" t="n"/>
-      <c r="C61" s="27" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="27" t="n"/>
-      <c r="F61" s="27" t="n"/>
-      <c r="G61" s="27" t="n"/>
-      <c r="H61" s="27" t="n"/>
-      <c r="I61" s="28" t="n"/>
-      <c r="J61" s="28" t="n"/>
-      <c r="K61" s="28" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="28" t="n"/>
+      <c r="A61" s="36" t="inlineStr">
+        <is>
+          <t>Kerlin Gallery</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="C61" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>179</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="H61" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="I61" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K61" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L61" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M61" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="N61" s="29" t="n"/>
-      <c r="O61" s="29" t="n"/>
-      <c r="P61" s="29" t="n"/>
+      <c r="O61" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P61" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q61" s="29" t="n"/>
       <c r="R61" s="29" t="n"/>
       <c r="S61" s="29" t="n"/>
@@ -4336,22 +4404,56 @@
       <c r="Z61" s="7" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="40">
-      <c r="A62" s="36" t="n"/>
-      <c r="B62" s="27" t="n"/>
-      <c r="C62" s="27" t="n"/>
-      <c r="D62" s="27" t="n"/>
-      <c r="E62" s="27" t="n"/>
-      <c r="F62" s="27" t="n"/>
-      <c r="G62" s="27" t="n"/>
-      <c r="H62" s="27" t="n"/>
-      <c r="I62" s="28" t="n"/>
-      <c r="J62" s="28" t="n"/>
-      <c r="K62" s="28" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="28" t="n"/>
+      <c r="A62" s="36" t="inlineStr">
+        <is>
+          <t>Tina Kim Gallery</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="C62" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D62" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>117</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="H62" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="I62" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" s="28" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="L62" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N62" s="29" t="n"/>
-      <c r="O62" s="29" t="n"/>
-      <c r="P62" s="29" t="n"/>
+      <c r="O62" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P62" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q62" s="29" t="n"/>
       <c r="R62" s="29" t="n"/>
       <c r="S62" s="29" t="n"/>
@@ -4364,22 +4466,60 @@
       <c r="Z62" s="7" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="40">
-      <c r="A63" s="36" t="n"/>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="27" t="n"/>
-      <c r="F63" s="27" t="n"/>
-      <c r="G63" s="27" t="n"/>
-      <c r="H63" s="27" t="n"/>
-      <c r="I63" s="28" t="n"/>
-      <c r="J63" s="28" t="n"/>
-      <c r="K63" s="28" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="28" t="n"/>
-      <c r="N63" s="29" t="n"/>
-      <c r="O63" s="29" t="n"/>
-      <c r="P63" s="29" t="n"/>
+      <c r="A63" s="36" t="inlineStr">
+        <is>
+          <t>Kukje Gallery</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="L63" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="N63" s="29" t="inlineStr">
+        <is>
+          <t>human_skip_after_verify_first</t>
+        </is>
+      </c>
+      <c r="O63" s="41" t="n">
+        <v>46155</v>
+      </c>
+      <c r="P63" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_SKIP_REFLECT_20260513</t>
+        </is>
+      </c>
       <c r="Q63" s="29" t="n"/>
       <c r="R63" s="29" t="n"/>
       <c r="S63" s="29" t="n"/>
@@ -4392,22 +4532,56 @@
       <c r="Z63" s="7" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="40">
-      <c r="A64" s="36" t="n"/>
-      <c r="B64" s="27" t="n"/>
-      <c r="C64" s="27" t="n"/>
-      <c r="D64" s="27" t="n"/>
-      <c r="E64" s="27" t="n"/>
-      <c r="F64" s="27" t="n"/>
-      <c r="G64" s="27" t="n"/>
-      <c r="H64" s="27" t="n"/>
-      <c r="I64" s="28" t="n"/>
-      <c r="J64" s="28" t="n"/>
-      <c r="K64" s="28" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="28" t="n"/>
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>Lehmann Maupin</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="C64" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <v>97.67441860465117</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>210</v>
+      </c>
+      <c r="G64" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="H64" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="I64" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="J64" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="28" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="L64" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M64" s="28" t="n">
+        <v>18</v>
+      </c>
       <c r="N64" s="29" t="n"/>
-      <c r="O64" s="29" t="n"/>
-      <c r="P64" s="29" t="n"/>
+      <c r="O64" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P64" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q64" s="29" t="n"/>
       <c r="R64" s="29" t="n"/>
       <c r="S64" s="29" t="n"/>
@@ -4420,22 +4594,56 @@
       <c r="Z64" s="7" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="40">
-      <c r="A65" s="36" t="n"/>
-      <c r="B65" s="27" t="n"/>
-      <c r="C65" s="27" t="n"/>
-      <c r="D65" s="27" t="n"/>
-      <c r="E65" s="27" t="n"/>
-      <c r="F65" s="27" t="n"/>
-      <c r="G65" s="27" t="n"/>
-      <c r="H65" s="27" t="n"/>
-      <c r="I65" s="28" t="n"/>
-      <c r="J65" s="28" t="n"/>
-      <c r="K65" s="28" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="28" t="n"/>
+      <c r="A65" s="36" t="inlineStr">
+        <is>
+          <t>Lisson Gallery</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="C65" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>336</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="H65" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="I65" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J65" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="28" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="L65" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="28" t="n">
+        <v>24</v>
+      </c>
       <c r="N65" s="29" t="n"/>
-      <c r="O65" s="29" t="n"/>
-      <c r="P65" s="29" t="n"/>
+      <c r="O65" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P65" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q65" s="29" t="n"/>
       <c r="R65" s="29" t="n"/>
       <c r="S65" s="29" t="n"/>
@@ -4448,22 +4656,56 @@
       <c r="Z65" s="7" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="40">
-      <c r="A66" s="36" t="n"/>
-      <c r="B66" s="27" t="n"/>
-      <c r="C66" s="27" t="n"/>
-      <c r="D66" s="27" t="n"/>
-      <c r="E66" s="27" t="n"/>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
-      <c r="H66" s="27" t="n"/>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="28" t="n"/>
-      <c r="K66" s="28" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="28" t="n"/>
+      <c r="A66" s="36" t="inlineStr">
+        <is>
+          <t>Kate MacGarry</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="C66" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="D66" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="F66" s="27" t="n">
+        <v>123</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="H66" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="I66" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J66" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L66" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" s="28" t="n">
+        <v>6</v>
+      </c>
       <c r="N66" s="29" t="n"/>
-      <c r="O66" s="29" t="n"/>
-      <c r="P66" s="29" t="n"/>
+      <c r="O66" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P66" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q66" s="29" t="n"/>
       <c r="R66" s="29" t="n"/>
       <c r="S66" s="29" t="n"/>
@@ -4476,22 +4718,56 @@
       <c r="Z66" s="7" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="40">
-      <c r="A67" s="36" t="n"/>
-      <c r="B67" s="27" t="n"/>
-      <c r="C67" s="27" t="n"/>
+      <c r="A67" s="36" t="inlineStr">
+        <is>
+          <t>Maisterravalbuena</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="D67" s="27" t="n"/>
-      <c r="E67" s="27" t="n"/>
-      <c r="F67" s="27" t="n"/>
-      <c r="G67" s="27" t="n"/>
-      <c r="H67" s="27" t="n"/>
-      <c r="I67" s="28" t="n"/>
-      <c r="J67" s="28" t="n"/>
+      <c r="E67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="K67" s="28" t="n"/>
-      <c r="L67" s="28" t="n"/>
-      <c r="M67" s="28" t="n"/>
-      <c r="N67" s="29" t="n"/>
-      <c r="O67" s="29" t="n"/>
-      <c r="P67" s="29" t="n"/>
+      <c r="L67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="29" t="inlineStr">
+        <is>
+          <t>human_skip_after_verify_first</t>
+        </is>
+      </c>
+      <c r="O67" s="41" t="n">
+        <v>46155</v>
+      </c>
+      <c r="P67" s="29" t="inlineStr">
+        <is>
+          <t>TASK_PHASE3_BLOCK_SKIP_REFLECT_20260513</t>
+        </is>
+      </c>
       <c r="Q67" s="29" t="n"/>
       <c r="R67" s="29" t="n"/>
       <c r="S67" s="29" t="n"/>
@@ -4504,22 +4780,56 @@
       <c r="Z67" s="7" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="40">
-      <c r="A68" s="36" t="n"/>
-      <c r="B68" s="27" t="n"/>
-      <c r="C68" s="27" t="n"/>
-      <c r="D68" s="27" t="n"/>
-      <c r="E68" s="27" t="n"/>
-      <c r="F68" s="27" t="n"/>
-      <c r="G68" s="27" t="n"/>
-      <c r="H68" s="27" t="n"/>
-      <c r="I68" s="28" t="n"/>
-      <c r="J68" s="28" t="n"/>
-      <c r="K68" s="28" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="28" t="n"/>
+      <c r="A68" s="36" t="inlineStr">
+        <is>
+          <t>Victoria Miro</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="C68" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="D68" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="F68" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="G68" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="H68" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="I68" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J68" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K68" s="28" t="n">
+        <v>30.43478260869565</v>
+      </c>
+      <c r="L68" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M68" s="28" t="n">
+        <v>22</v>
+      </c>
       <c r="N68" s="29" t="n"/>
-      <c r="O68" s="29" t="n"/>
-      <c r="P68" s="29" t="n"/>
+      <c r="O68" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q68" s="29" t="n"/>
       <c r="R68" s="29" t="n"/>
       <c r="S68" s="29" t="n"/>
@@ -4532,22 +4842,56 @@
       <c r="Z68" s="7" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="40">
-      <c r="A69" s="36" t="n"/>
-      <c r="B69" s="27" t="n"/>
-      <c r="C69" s="27" t="n"/>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="27" t="n"/>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-      <c r="I69" s="28" t="n"/>
-      <c r="J69" s="28" t="n"/>
-      <c r="K69" s="28" t="n"/>
-      <c r="L69" s="28" t="n"/>
-      <c r="M69" s="28" t="n"/>
+      <c r="A69" s="36" t="inlineStr">
+        <is>
+          <t>mor charpentier</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="C69" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="D69" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="F69" s="27" t="n">
+        <v>154</v>
+      </c>
+      <c r="G69" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="H69" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="I69" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" s="28" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="L69" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M69" s="28" t="n">
+        <v>7</v>
+      </c>
       <c r="N69" s="29" t="n"/>
-      <c r="O69" s="29" t="n"/>
-      <c r="P69" s="29" t="n"/>
+      <c r="O69" s="41" t="n">
+        <v>46156</v>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>p3_next_real_20260512</t>
+        </is>
+      </c>
       <c r="Q69" s="29" t="n"/>
       <c r="R69" s="29" t="n"/>
       <c r="S69" s="29" t="n"/>
